--- a/public/roster-template.xlsx
+++ b/public/roster-template.xlsx
@@ -136,7 +136,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -156,19 +156,19 @@
       <c r="D1" s="1"/>
     </row>
     <row r="2" ht="21" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>보호자 서면 동의를 받은 학생만 적어 주세요.</t>
-        </is>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>4개 열의 이름과 순서를 바꾸면 파일을 읽을 수 없어요.</t>
+        </is>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
     </row>
     <row r="3" ht="21" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>4개 열의 이름과 순서는 바꾸지 마세요.</t>
+          <t>번호는 숫자만 적어 주세요 — 2-1처럼 반을 붙이면 안 돼요.</t>
         </is>
       </c>
       <c r="B3" s="2"/>
@@ -178,45 +178,46 @@
     <row r="4" ht="21" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>줄이 부족하면 아래로 얼마든지 늘려도 됩니다.</t>
+          <t>생년월일은 2019-03-04처럼 적어 주세요.</t>
         </is>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" ht="21" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>주민등록번호는 넣지 마세요 — 넣어도 저장되지 않습니다.</t>
-        </is>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6" ht="10" customHeight="1"/>
-    <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>번호</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>이름</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>성별</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>생년월일</t>
         </is>
       </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="5"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="5"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="5"/>
@@ -416,28 +417,15 @@
       <c r="C40" s="5"/>
       <c r="D40" s="5"/>
     </row>
-    <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="5"/>
-      <c r="B41" s="6"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
-    </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="5"/>
-      <c r="B42" s="6"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
-    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A5:D5"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C8:C42">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C6:C40">
       <formula1>"남,여"</formula1>
     </dataValidation>
   </dataValidations>

--- a/public/roster-template.xlsx
+++ b/public/roster-template.xlsx
@@ -22,13 +22,14 @@
       <name val="맑은 고딕"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF3A4256"/>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF0E1526"/>
       <name val="맑은 고딕"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="12"/>
       <color rgb="FF96660C"/>
       <name val="맑은 고딕"/>
     </font>
@@ -155,7 +156,7 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" ht="21" customHeight="1">
+    <row r="2" ht="26" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
           <t>4개 열의 이름과 순서를 바꾸면 파일을 읽을 수 없어요.</t>
@@ -165,7 +166,7 @@
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
     </row>
-    <row r="3" ht="21" customHeight="1">
+    <row r="3" ht="26" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>번호는 숫자만 적어 주세요 — 2-1처럼 반을 붙이면 안 돼요.</t>
@@ -175,7 +176,7 @@
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
     </row>
-    <row r="4" ht="21" customHeight="1">
+    <row r="4" ht="26" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>생년월일은 2019-03-04처럼 적어 주세요.</t>

--- a/public/roster-template.xlsx
+++ b/public/roster-template.xlsx
@@ -179,7 +179,7 @@
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>생년월일은 2019-03-04처럼 적어 주세요.</t>
+          <t>생년월일은 연도를 먼저 — 2019-03-04 · 190304 다 괜찮아요.</t>
         </is>
       </c>
       <c r="B4" s="2"/>

--- a/public/roster-template.xlsx
+++ b/public/roster-template.xlsx
@@ -144,6 +144,7 @@
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="16384" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
